--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484056_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484056_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0511</v>
+        <v>5.4408</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2203</v>
+        <v>6.4697</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1692</v>
+        <v>-1.0289</v>
       </c>
       <c r="G2" t="n">
         <v>3.2941</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2692</v>
+        <v>0.1205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0511</v>
+        <v>0.3005</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3203</v>
+        <v>-0.1801</v>
       </c>
       <c r="V2" t="n">
         <v>1.8278</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0919</v>
+        <v>1.3404</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4049</v>
+        <v>0.5693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7712</v>
       </c>
       <c r="G3" t="n">
         <v>0.0042</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1819</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0057</v>
+        <v>0.1701</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1877</v>
+        <v>-0.1035</v>
       </c>
       <c r="V3" t="n">
         <v>0.6745</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9261</v>
+        <v>1.2037</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9182</v>
+        <v>3.1922</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.9921</v>
+        <v>-1.9884</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8396</v>
+        <v>-1.5546</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0711</v>
+        <v>-2.6817</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9107</v>
+        <v>1.1271</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0241</v>
+        <v>2.8305</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4232</v>
+        <v>0.9327</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3991</v>
+        <v>1.8978</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.8638</v>
+        <v>-4.3852</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.3521</v>
+        <v>-3.6144</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5117</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>2.422</v>
+        <v>-0.0496</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5362</v>
+        <v>-0.1189</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8858</v>
+        <v>0.0693</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4579</v>
+        <v>1.4192</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3417</v>
+        <v>1.4724</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7996</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7158</v>
+        <v>1.0206</v>
       </c>
       <c r="E5" t="n">
-        <v>1.882</v>
+        <v>3.3407</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1662</v>
+        <v>-2.3201</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7056</v>
+        <v>1.1979</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1643</v>
+        <v>-1.5979</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4587</v>
+        <v>2.7958</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0925</v>
+        <v>4.1912</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1626</v>
+        <v>1.0134</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0701</v>
+        <v>3.1779</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3869</v>
+        <v>-2.9933</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9983</v>
+        <v>-2.6112</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3886</v>
+        <v>-0.3821</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8671</v>
+        <v>-1.0486</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2334</v>
+        <v>-0.1246</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3662</v>
+        <v>-0.924</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2698</v>
+        <v>-0.1206</v>
       </c>
       <c r="W5" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8018</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5907</v>
+        <v>-0.644</v>
       </c>
       <c r="E6" t="n">
-        <v>2.495</v>
+        <v>0.5783</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9043</v>
+        <v>-1.2223</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5546</v>
+        <v>0.7056</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6817</v>
+        <v>1.1643</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1271</v>
+        <v>-0.4587</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8305</v>
+        <v>2.0925</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9327</v>
+        <v>2.1626</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8978</v>
+        <v>-0.0701</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.3852</v>
+        <v>-1.3869</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.6144</v>
+        <v>-0.9983</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3886</v>
       </c>
       <c r="P6" t="n">
+        <v>-1.5871</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.9758</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.3887</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3806</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.6626</v>
+        <v>0.5073</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8161</v>
+        <v>0.9296</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1535</v>
+        <v>-0.4223</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4192</v>
+        <v>-0.2698</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4724</v>
+        <v>0.532</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0532</v>
+        <v>-0.8018</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0593</v>
+        <v>-0.7279</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6038</v>
+        <v>-0.1247</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5445</v>
+        <v>-0.6032</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1979</v>
+        <v>-0.4672</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5979</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7958</v>
+        <v>-0.4016</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1912</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0134</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1779</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9933</v>
+        <v>-0.4672</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.6112</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3821</v>
+        <v>-0.4016</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0099</v>
+        <v>-0.2607</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8615</v>
+        <v>-0.1247</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1484</v>
+        <v>-0.136</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7279</v>
+        <v>-0.8086</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1247</v>
+        <v>3.7165</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6032</v>
+        <v>-4.5251</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4672</v>
+        <v>-0.8396</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0711</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4016</v>
+        <v>-0.9107</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3.0241</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.4232</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.3991</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4672</v>
+        <v>-3.8638</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-3.3521</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4016</v>
+        <v>-0.5117</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2607</v>
+        <v>0.6873</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1247</v>
+        <v>0.3345</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.136</v>
+        <v>0.3527</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.4579</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.3417</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.7996</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3645</v>
+        <v>-1.1126</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8801</v>
+        <v>0.3006</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4844</v>
+        <v>-1.4132</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9125</v>
+        <v>-2.3074</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1288</v>
+        <v>-1.9304</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2164</v>
+        <v>-0.377</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5797</v>
+        <v>0.2269</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.66</v>
+        <v>-0.4584</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0803</v>
+        <v>0.6853</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3328</v>
+        <v>-2.5343</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4688</v>
+        <v>-1.472</v>
       </c>
       <c r="O9" t="n">
-        <v>0.136</v>
+        <v>-1.0623</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6751</v>
+        <v>-0.0071</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6915</v>
+        <v>0.0737</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0165</v>
+        <v>-0.0808</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.532</v>
+        <v>0.21</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.532</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9438</v>
+        <v>-1.7548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3342</v>
+        <v>-1.1862</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6096</v>
+        <v>-0.5686</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3074</v>
+        <v>-0.9125</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9304</v>
+        <v>-1.1288</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.377</v>
+        <v>0.2164</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2269</v>
+        <v>-0.5797</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4584</v>
+        <v>-0.66</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6853</v>
+        <v>0.0803</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5343</v>
+        <v>-0.3328</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.472</v>
+        <v>-0.4688</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0623</v>
+        <v>0.136</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8383</v>
+        <v>0.2848</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5611</v>
+        <v>0.3855</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2772</v>
+        <v>-0.1006</v>
       </c>
       <c r="V10" t="n">
-        <v>0.21</v>
+        <v>-0.532</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.21</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9928</v>
+        <v>-2.8835</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9821</v>
+        <v>-0.0412</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0107</v>
+        <v>-2.8423</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0633</v>
@@ -1312,13 +1312,13 @@
         <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4635</v>
+        <v>-0.3542</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1222</v>
+        <v>-0.1813</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3413</v>
+        <v>-0.173</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4579</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4286</v>
+        <v>-3.8499</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4559</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9727</v>
+        <v>-3.0288</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2356</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7799</v>
+        <v>-0.2012</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5498</v>
+        <v>0.0851</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2302</v>
+        <v>-0.2863</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6115</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0227</v>
+        <v>-2.7758</v>
       </c>
       <c r="E13" t="n">
-        <v>14.7472</v>
+        <v>15.9941</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.7699</v>
+        <v>-18.7697</v>
       </c>
       <c r="G13" t="n">
         <v>-5.1784</v>
@@ -1468,13 +1468,13 @@
         <v>15.8707</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.501799999999999</v>
+        <v>-0.2549</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4825</v>
+        <v>1.7295</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9845</v>
+        <v>-1.9846</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3182</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0341</v>
+        <v>3.5994</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5242</v>
+        <v>5.8772</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.49</v>
+        <v>-2.2778</v>
       </c>
       <c r="G14" t="n">
-        <v>0.698</v>
+        <v>2.5121</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7057</v>
+        <v>-0.136</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0077</v>
+        <v>2.6481</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7374</v>
+        <v>6.0415</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9744</v>
+        <v>2.344</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7631</v>
+        <v>3.6974</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0394</v>
+        <v>-3.5294</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2687</v>
+        <v>-2.4801</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.0493</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4074</v>
+        <v>-0.1743</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9807</v>
+        <v>-0.1643</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4267</v>
+        <v>-0.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1352</v>
+        <v>0.0713</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3373</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0612</v>
+        <v>3.364</v>
       </c>
       <c r="E15" t="n">
-        <v>5.367</v>
+        <v>4.2801</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3058</v>
+        <v>-0.9162</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5121</v>
+        <v>4.348</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.136</v>
+        <v>3.971</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6481</v>
+        <v>0.377</v>
       </c>
       <c r="J15" t="n">
-        <v>6.0415</v>
+        <v>5.5501</v>
       </c>
       <c r="K15" t="n">
-        <v>2.344</v>
+        <v>4.4154</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6974</v>
+        <v>1.1347</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5294</v>
+        <v>-1.2021</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4801</v>
+        <v>-0.4444</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0493</v>
+        <v>-0.7577</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7125</v>
+        <v>0.2224</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6744</v>
+        <v>0.4479</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.038</v>
+        <v>-0.2255</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0713</v>
+        <v>-1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0713</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0775</v>
+        <v>2.9654</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1578</v>
+        <v>3.7079</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0803</v>
+        <v>-0.7425</v>
       </c>
       <c r="G16" t="n">
-        <v>4.348</v>
+        <v>0.698</v>
       </c>
       <c r="H16" t="n">
-        <v>3.971</v>
+        <v>0.7057</v>
       </c>
       <c r="I16" t="n">
-        <v>0.377</v>
+        <v>-0.0077</v>
       </c>
       <c r="J16" t="n">
-        <v>5.5501</v>
+        <v>3.7374</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4154</v>
+        <v>2.9744</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1347</v>
+        <v>0.7631</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2021</v>
+        <v>-3.0394</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4444</v>
+        <v>-2.2687</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7577</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.064</v>
+        <v>0.3387</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6744</v>
+        <v>0.1645</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3896</v>
+        <v>0.1742</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2065</v>
+        <v>1.1352</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4724</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9085</v>
+        <v>0.2565</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7263</v>
+        <v>0.3125</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8178</v>
+        <v>-0.056</v>
       </c>
       <c r="G17" t="n">
-        <v>2.344</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.344</v>
+        <v>0.3776</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.2269</v>
       </c>
       <c r="J17" t="n">
-        <v>2.344</v>
+        <v>0.1262</v>
       </c>
       <c r="K17" t="n">
-        <v>2.344</v>
+        <v>0.1613</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.0351</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-0.9756</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.2163</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.1918</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6952</v>
+        <v>0.0978</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0406</v>
+        <v>-0.0283</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6546</v>
+        <v>0.1261</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1469</v>
+        <v>1.2065</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.161</v>
+        <v>0.2172</v>
       </c>
       <c r="E18" t="n">
         <v>1.6661</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5051</v>
+        <v>-1.4489</v>
       </c>
       <c r="G18" t="n">
         <v>0.3107</v>
@@ -1858,13 +1858,13 @@
         <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.348</v>
+        <v>-0.2919</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2494</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0425</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>G. RODRIGUEZ FLAQUE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1454</v>
+        <v>0.1081</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3009</v>
+        <v>0.3872</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1555</v>
+        <v>-0.2791</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1577</v>
+        <v>-0.7459</v>
       </c>
       <c r="H19" t="n">
-        <v>1.139</v>
+        <v>0.8515</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2968</v>
+        <v>-1.5974</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1539</v>
+        <v>-0.1736</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9932</v>
+        <v>0.504</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1606</v>
+        <v>-0.6776</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3116</v>
+        <v>-0.5723</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1458</v>
+        <v>0.3474</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4574</v>
+        <v>-0.9198</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7594</v>
+        <v>-0.0071</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8649</v>
+        <v>0.2948</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1055</v>
+        <v>-0.3019</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.266</v>
+        <v>0.266</v>
       </c>
       <c r="W19" t="n">
         <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2047</v>
+        <v>0.0793</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2806</v>
+        <v>-0.0766</v>
       </c>
       <c r="F20" t="n">
-        <v>0.076</v>
+        <v>0.1559</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4247</v>
@@ -2014,13 +2014,13 @@
         <v>0.1984</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1848</v>
+        <v>0.0992</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.187</v>
+        <v>0.017</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0022</v>
+        <v>0.0822</v>
       </c>
       <c r="V20" t="n">
         <v>1.2065</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4279</v>
+        <v>0.0515</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0956</v>
+        <v>3.4199</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3323</v>
+        <v>-3.3684</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8493000000000001</v>
+        <v>1.6966</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3776</v>
+        <v>0.2067</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2269</v>
+        <v>1.4899</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1262</v>
+        <v>5.1442</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1613</v>
+        <v>2.6114</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0351</v>
+        <v>2.5327</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9756</v>
+        <v>-3.4475</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2163</v>
+        <v>-2.4047</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1918</v>
+        <v>-1.0428</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5867</v>
+        <v>-0.316</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4364</v>
+        <v>-0.221</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1503</v>
+        <v>-0.095</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2065</v>
+        <v>-0.3373</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>1.4724</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ FLAQUE</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4964</v>
+        <v>-0.5964</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.021</v>
+        <v>0.5019</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4755</v>
+        <v>-1.0984</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7459</v>
+        <v>2.344</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8515</v>
+        <v>2.344</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5974</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1736</v>
+        <v>2.344</v>
       </c>
       <c r="K22" t="n">
-        <v>0.504</v>
+        <v>2.344</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6776</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5723</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3474</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9198</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5952</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6116</v>
+        <v>1.1903</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1133</v>
+        <v>0.8162</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4983</v>
+        <v>0.3741</v>
       </c>
       <c r="V22" t="n">
-        <v>0.266</v>
+        <v>-2.1469</v>
       </c>
       <c r="W22" t="n">
-        <v>0.266</v>
+        <v>-0.6745</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,75 +2203,71 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9152</v>
+        <v>-0.897</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7057</v>
+        <v>0.1786</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6209</v>
+        <v>-1.0756</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6966</v>
+        <v>-0.1577</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2067</v>
+        <v>1.139</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4899</v>
+        <v>-1.2968</v>
       </c>
       <c r="J23" t="n">
-        <v>5.1442</v>
+        <v>1.1539</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6114</v>
+        <v>0.9932</v>
       </c>
       <c r="L23" t="n">
-        <v>2.5327</v>
+        <v>0.1606</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.4475</v>
+        <v>-1.3116</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4047</v>
+        <v>0.1458</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0428</v>
+        <v>-1.4574</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2827</v>
+        <v>0.717</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9352</v>
+        <v>0.7426</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3475</v>
+        <v>-0.0256</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.8097</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>E. MAÑES CARRETERO</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2281,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0606</v>
+        <v>-1.5995</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9996</v>
+        <v>0.1269</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.061</v>
+        <v>-1.7264</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.966</v>
+        <v>-2.5872</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6189</v>
+        <v>-1.3863</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.5849</v>
+        <v>-1.2009</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3721</v>
+        <v>0.3423</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5321</v>
+        <v>0.2218</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.16</v>
+        <v>0.1205</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3381</v>
+        <v>-2.9294</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9132</v>
+        <v>-1.608</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4249</v>
+        <v>-1.3214</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.579</v>
+        <v>0.9919</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.9596</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3806</v>
+        <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>1.095</v>
+        <v>-0.0042</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9921</v>
+        <v>-0.2153</v>
       </c>
       <c r="U24" t="n">
-        <v>0.103</v>
+        <v>0.2111</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3894</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5959</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2601</v>
+        <v>-1.5995</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2812</v>
+        <v>0.1269</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9789</v>
+        <v>-1.7264</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5872</v>
@@ -2404,13 +2400,13 @@
         <v>0.9919</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6649</v>
+        <v>-0.0042</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0414</v>
+        <v>0.2111</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2423,7 +2419,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E. MAÑES CARRETERO</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2433,67 +2433,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.2601</v>
+        <v>-2.399</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2812</v>
+        <v>-1.3057</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9789</v>
+        <v>-1.0933</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.5872</v>
+        <v>-0.966</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3863</v>
+        <v>3.6189</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2009</v>
+        <v>-4.5849</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3423</v>
+        <v>1.3721</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2218</v>
+        <v>4.5321</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1205</v>
+        <v>-3.16</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9294</v>
+        <v>-2.3381</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.608</v>
+        <v>-0.9132</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.3214</v>
+        <v>-1.4249</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9919</v>
+        <v>-2.579</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-4.9596</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6649</v>
+        <v>0.7567</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0414</v>
+        <v>0.0707</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.3894</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.5959</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="27">
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.7627</v>
+        <v>3.549999999999998</v>
       </c>
       <c r="E27" t="n">
-        <v>18.4888</v>
+        <v>19.2029</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.726</v>
+        <v>-15.6531</v>
       </c>
       <c r="G27" t="n">
         <v>2.591399999999999</v>
@@ -2556,19 +2556,19 @@
         <v>13.8868</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8368999999999995</v>
+        <v>2.6244</v>
       </c>
       <c r="T27" t="n">
-        <v>1.3612</v>
+        <v>2.0754</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5241</v>
+        <v>0.549</v>
       </c>
       <c r="V27" t="n">
-        <v>0.3182000000000003</v>
+        <v>0.3181999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>6.4027</v>
+        <v>6.402699999999999</v>
       </c>
       <c r="X27" t="n">
         <v>-6.0844</v>
